--- a/table.xlsx
+++ b/table.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -457,40 +457,41 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
+        <v>整车配置</v>
+      </c>
+      <c r="C3" t="str">
+        <v>DH3整车配置表</v>
+      </c>
+      <c r="D3" t="str">
+        <v>https://acndoaymjsa1.feishu.cn/file/FzRlbkP7Yo5xvfxqIwmcYXzmn0c</v>
+      </c>
+      <c r="E3" t="str">
+        <v>url</v>
+      </c>
+      <c r="F3" t="str" xml:space="preserve">
+        <v xml:space="preserve">飞书，DH3整车配置表
+11月14日版本</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
         <v>设计评审</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C4" t="str">
         <v>DH3电子电气拓扑图</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D4" t="str">
         <v>w:\yling</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E4" t="str">
         <v>folder</v>
       </c>
-      <c r="F3" t="str" xml:space="preserve">
+      <c r="F4" t="str" xml:space="preserve">
         <v xml:space="preserve">内网，w:\yling
 请确保你的账号已经切换到内网</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>阶段评审</v>
-      </c>
-      <c r="C4" t="str">
-        <v>DH3项目J2阶段评审材料归档路径</v>
-      </c>
-      <c r="D4" t="str">
-        <v>\\10.4.9.25\Project\DH系列\130-智能软件\DH3\130100_ 阶段评审材料\130102_ J2阶段评审材料及会议纪要</v>
-      </c>
-      <c r="E4" t="str">
-        <v>folder</v>
-      </c>
-      <c r="F4" t="str">
-        <v>外网，请大家把J2材料及会议纪要放入此文件夹</v>
       </c>
     </row>
     <row r="5">
@@ -498,19 +499,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>开发计划</v>
+        <v>阶段评审</v>
       </c>
       <c r="C5" t="str">
-        <v>DH3项目智软控制器开发计划</v>
+        <v>DH3项目J2阶段评审材料归档路径</v>
       </c>
       <c r="D5" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/file/K8KlbxqKmoZV2HxoG94ccLotnne</v>
+        <v>\\10.4.9.25\Project\DH系列\130-智能软件\DH3\130100_ 阶段评审材料\130102_ J2阶段评审材料及会议纪要</v>
       </c>
       <c r="E5" t="str">
-        <v>url</v>
+        <v>folder</v>
       </c>
       <c r="F5" t="str">
-        <v>飞书，请大家在此更新各自开发计划</v>
+        <v>外网，请大家把J2材料及会议纪要放入此文件夹</v>
       </c>
     </row>
     <row r="6">
@@ -518,19 +519,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>阶段评审</v>
+        <v>开发计划</v>
       </c>
       <c r="C6" t="str">
-        <v>DH3项目J2阶段评审材料输入信息</v>
+        <v>DH3项目智软控制器开发计划</v>
       </c>
       <c r="D6" t="str">
-        <v>\\10.4.9.25\Project\DH系列\060-整车开发\DH3\J2评审输入</v>
+        <v>https://acndoaymjsa1.feishu.cn/file/K8KlbxqKmoZV2HxoG94ccLotnne</v>
       </c>
       <c r="E6" t="str">
-        <v>folder</v>
+        <v>url</v>
       </c>
       <c r="F6" t="str">
-        <v>外网，J2阶段输入物数据库</v>
+        <v>飞书，请大家在此更新各自开发计划</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +539,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>联系信息</v>
+        <v>阶段评审</v>
       </c>
       <c r="C7" t="str">
-        <v>DH项目联系清单</v>
+        <v>DH3项目J2阶段评审材料输入信息</v>
       </c>
       <c r="D7" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/sheets/Gbh8sTDmdhMD9DtZcC2c7trunRe</v>
+        <v>\\10.4.9.25\Project\DH系列\060-整车开发\DH3\J2评审输入</v>
       </c>
       <c r="E7" t="str">
-        <v>url</v>
+        <v>folder</v>
       </c>
       <c r="F7" t="str">
-        <v>飞书，DH项目整体联系人</v>
+        <v>外网，J2阶段输入物数据库</v>
       </c>
     </row>
     <row r="8">
@@ -561,16 +562,16 @@
         <v>联系信息</v>
       </c>
       <c r="C8" t="str">
-        <v>DH3项目华为接口联系人清单</v>
+        <v>DH项目联系清单</v>
       </c>
       <c r="D8" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/file/NI95bmHjpoopKBxVGhrc7S9SnUc</v>
+        <v>https://acndoaymjsa1.feishu.cn/sheets/Gbh8sTDmdhMD9DtZcC2c7trunRe</v>
       </c>
       <c r="E8" t="str">
         <v>url</v>
       </c>
       <c r="F8" t="str">
-        <v>飞书，包含华为座舱、智驾、网联相关接口人信息</v>
+        <v>飞书，DH项目整体联系人</v>
       </c>
     </row>
     <row r="9">
@@ -581,16 +582,16 @@
         <v>联系信息</v>
       </c>
       <c r="C9" t="str">
-        <v>DH3项目研发总院智软内部责任分工</v>
+        <v>DH3项目华为接口联系人清单</v>
       </c>
       <c r="D9" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/wiki/YyMcwejHNifAkfk0aEXcjdeQnTb?table=tbltH0YNXCFoOxNm&amp;view=vewS54CcOf</v>
+        <v>https://acndoaymjsa1.feishu.cn/file/NI95bmHjpoopKBxVGhrc7S9SnUc</v>
       </c>
       <c r="E9" t="str">
         <v>url</v>
       </c>
       <c r="F9" t="str">
-        <v>飞书，仅包含东风研发总院智软内部相关责任人分工，仅智软群成员可访问</v>
+        <v>飞书，包含华为座舱、智驾、网联相关接口人信息</v>
       </c>
     </row>
     <row r="10">
@@ -598,19 +599,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>再发防止</v>
+        <v>联系信息</v>
       </c>
       <c r="C10" t="str">
-        <v>DH3 LLR与PRC再发防止 - 总院级</v>
+        <v>DH3项目研发总院智软内部责任分工</v>
       </c>
       <c r="D10" t="str">
-        <v>https://doc.weixin.qq.com/sheet/e3_AKkAcQbnAKcCNoUhJadOcRr27t3Mb?scode=AGwAPQeYAA0i5kLUWBAbgALQaUAJ8&amp;version=5.0.0.8619&amp;platform=win&amp;tab=mfripw</v>
+        <v>https://acndoaymjsa1.feishu.cn/wiki/YyMcwejHNifAkfk0aEXcjdeQnTb?table=tbltH0YNXCFoOxNm&amp;view=vewS54CcOf</v>
       </c>
       <c r="E10" t="str">
         <v>url</v>
       </c>
       <c r="F10" t="str">
-        <v>企微，DH3 LLR与PRC再发防止 - 总院级</v>
+        <v>飞书，仅包含东风研发总院智软内部相关责任人分工，仅智软群成员可访问</v>
       </c>
     </row>
     <row r="11">
@@ -621,21 +622,41 @@
         <v>再发防止</v>
       </c>
       <c r="C11" t="str">
+        <v>DH3 LLR与PRC再发防止 - 总院级</v>
+      </c>
+      <c r="D11" t="str">
+        <v>https://doc.weixin.qq.com/sheet/e3_AKkAcQbnAKcCNoUhJadOcRr27t3Mb?scode=AGwAPQeYAA0i5kLUWBAbgALQaUAJ8&amp;version=5.0.0.8619&amp;platform=win&amp;tab=mfripw</v>
+      </c>
+      <c r="E11" t="str">
+        <v>url</v>
+      </c>
+      <c r="F11" t="str">
+        <v>企微，DH3 LLR与PRC再发防止 - 总院级</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>再发防止</v>
+      </c>
+      <c r="C12" t="str">
         <v>DH3不满再发防止 - 整车级</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D12" t="str">
         <v>https://acndoaymjsa1.feishu.cn/file/BzEsbuCLCowqs2xT1y0cRe1JnSb</v>
       </c>
-      <c r="E11" t="str">
-        <v>url</v>
-      </c>
-      <c r="F11" t="str">
+      <c r="E12" t="str">
+        <v>url</v>
+      </c>
+      <c r="F12" t="str">
         <v>飞书，DH3不满再发防止 - 整车级</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/table.xlsx
+++ b/table.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -448,7 +444,7 @@
         <v>url</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">飞书，DH3项目主计划
+        <v xml:space="preserve">【飞书】DH3项目主计划
 10月9日版本</v>
       </c>
     </row>
@@ -460,58 +456,58 @@
         <v>整车配置</v>
       </c>
       <c r="C3" t="str">
-        <v>DH3整车配置表</v>
+        <v>DH3整车配置清单</v>
       </c>
       <c r="D3" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/file/FzRlbkP7Yo5xvfxqIwmcYXzmn0c</v>
+        <v>https://acndoaymjsa1.feishu.cn/file/R9ZGbDYjxoPqwwxpzNzcfeObnZg?from=from_copylink</v>
       </c>
       <c r="E3" t="str">
         <v>url</v>
       </c>
       <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">飞书，DH3整车配置表
-11月14日版本</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
+        <v xml:space="preserve">【飞书】DH3整车配置表
+11月20日版本</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>设计评审</v>
+        <v>联系信息</v>
       </c>
       <c r="C4" t="str">
-        <v>DH3电子电气拓扑图</v>
+        <v>DH项目整体联系人清单</v>
       </c>
       <c r="D4" t="str">
-        <v>w:\yling</v>
+        <v>https://acndoaymjsa1.feishu.cn/sheets/Gbh8sTDmdhMD9DtZcC2c7trunRe</v>
       </c>
       <c r="E4" t="str">
-        <v>folder</v>
-      </c>
-      <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">内网，w:\yling
-请确保你的账号已经切换到内网</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>url</v>
+      </c>
+      <c r="F4" t="str">
+        <v>【飞书】包含DH1，DH3各业务板块联系人信息</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>阶段评审</v>
+        <v>设计评审</v>
       </c>
       <c r="C5" t="str">
-        <v>DH3项目J2阶段评审材料归档路径</v>
+        <v>DH3电子电气拓扑图</v>
       </c>
       <c r="D5" t="str">
-        <v>\\10.4.9.25\Project\DH系列\130-智能软件\DH3\130100_ 阶段评审材料\130102_ J2阶段评审材料及会议纪要</v>
+        <v>w:\yling</v>
       </c>
       <c r="E5" t="str">
         <v>folder</v>
       </c>
-      <c r="F5" t="str">
-        <v>外网，请大家把J2材料及会议纪要放入此文件夹</v>
+      <c r="F5" t="str" xml:space="preserve">
+        <v xml:space="preserve">【内网】w:\yling
+请确保你的账号已经切换到内网</v>
       </c>
     </row>
     <row r="6">
@@ -519,19 +515,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>开发计划</v>
+        <v>阶段评审</v>
       </c>
       <c r="C6" t="str">
-        <v>DH3项目智软控制器开发计划</v>
+        <v>DH3项目J2阶段评审材料输入信息</v>
       </c>
       <c r="D6" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/file/K8KlbxqKmoZV2HxoG94ccLotnne</v>
+        <v>\\10.4.9.25\Project\DH系列\060-整车开发\DH3\J2评审输入</v>
       </c>
       <c r="E6" t="str">
-        <v>url</v>
+        <v>folder</v>
       </c>
       <c r="F6" t="str">
-        <v>飞书，请大家在此更新各自开发计划</v>
+        <v>【外网】J2阶段输入物数据库</v>
       </c>
     </row>
     <row r="7">
@@ -542,16 +538,16 @@
         <v>阶段评审</v>
       </c>
       <c r="C7" t="str">
-        <v>DH3项目J2阶段评审材料输入信息</v>
+        <v>DH3项目J2阶段评审材料归档路径</v>
       </c>
       <c r="D7" t="str">
-        <v>\\10.4.9.25\Project\DH系列\060-整车开发\DH3\J2评审输入</v>
+        <v>\\10.4.9.25\Project\DH系列\130-智能软件\DH3\130100_ 阶段评审材料\130102_ J2阶段评审材料及会议纪要</v>
       </c>
       <c r="E7" t="str">
         <v>folder</v>
       </c>
       <c r="F7" t="str">
-        <v>外网，J2阶段输入物数据库</v>
+        <v>【外网】请大家把J2材料及会议纪要放入此文件夹</v>
       </c>
     </row>
     <row r="8">
@@ -559,19 +555,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>联系信息</v>
+        <v>开发计划</v>
       </c>
       <c r="C8" t="str">
-        <v>DH项目联系清单</v>
+        <v>DH3项目智软控制器开发计划</v>
       </c>
       <c r="D8" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/sheets/Gbh8sTDmdhMD9DtZcC2c7trunRe</v>
+        <v>https://acndoaymjsa1.feishu.cn/file/K8KlbxqKmoZV2HxoG94ccLotnne</v>
       </c>
       <c r="E8" t="str">
         <v>url</v>
       </c>
       <c r="F8" t="str">
-        <v>飞书，DH项目整体联系人</v>
+        <v>【飞书】请大家在此更新各自开发计划</v>
       </c>
     </row>
     <row r="9">
@@ -591,7 +587,7 @@
         <v>url</v>
       </c>
       <c r="F9" t="str">
-        <v>飞书，包含华为座舱、智驾、网联相关接口人信息</v>
+        <v>【飞书】包含华为座舱、智驾、网联相关接口人信息</v>
       </c>
     </row>
     <row r="10">
@@ -611,7 +607,7 @@
         <v>url</v>
       </c>
       <c r="F10" t="str">
-        <v>飞书，仅包含东风研发总院智软内部相关责任人分工，仅智软群成员可访问</v>
+        <v>【飞书】仅包含东风研发总院智软内部相关责任人分工，仅智软群成员可访问</v>
       </c>
     </row>
     <row r="11">
@@ -622,16 +618,16 @@
         <v>再发防止</v>
       </c>
       <c r="C11" t="str">
-        <v>DH3 LLR与PRC再发防止 - 总院级</v>
+        <v>DH3不满再发防止-整车级</v>
       </c>
       <c r="D11" t="str">
-        <v>https://doc.weixin.qq.com/sheet/e3_AKkAcQbnAKcCNoUhJadOcRr27t3Mb?scode=AGwAPQeYAA0i5kLUWBAbgALQaUAJ8&amp;version=5.0.0.8619&amp;platform=win&amp;tab=mfripw</v>
+        <v>https://acndoaymjsa1.feishu.cn/file/BzEsbuCLCowqs2xT1y0cRe1JnSb</v>
       </c>
       <c r="E11" t="str">
         <v>url</v>
       </c>
       <c r="F11" t="str">
-        <v>企微，DH3 LLR与PRC再发防止 - 总院级</v>
+        <v>【飞书】DH3不满再发防止-整车级</v>
       </c>
     </row>
     <row r="12">
@@ -642,16 +638,16 @@
         <v>再发防止</v>
       </c>
       <c r="C12" t="str">
-        <v>DH3不满再发防止 - 整车级</v>
+        <v>DH3 LLR和PRC再发防止 - 总院级</v>
       </c>
       <c r="D12" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/file/BzEsbuCLCowqs2xT1y0cRe1JnSb</v>
+        <v>https://doc.weixin.qq.com/sheet/e3_AKkAcQbnAKcCNoUhJadOcRr27t3Mb?scode=AGwAPQeYAA0i5kLUWBAbgALQaUAJ8&amp;version=5.0.0.8619&amp;platform=win&amp;tab=mfripw</v>
       </c>
       <c r="E12" t="str">
         <v>url</v>
       </c>
       <c r="F12" t="str">
-        <v>飞书，DH3不满再发防止 - 整车级</v>
+        <v>【企微】DH3 LLR和PRC再发防止 - 总院级</v>
       </c>
     </row>
   </sheetData>

--- a/table.xlsx
+++ b/table.xlsx
@@ -438,14 +438,14 @@
         <v>DH3项目主计划</v>
       </c>
       <c r="D2" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/slides/QCyasDe1zlyqN1d1kJAcX753n2d</v>
+        <v>https://acndoaymjsa1.feishu.cn/file/JauUbijsxoJ4euxYl2Zc1ohunRb?from=from_copylink</v>
       </c>
       <c r="E2" t="str">
         <v>url</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
         <v xml:space="preserve">【飞书】DH3项目主计划
-10月9日版本</v>
+12月8日版本</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -459,14 +459,14 @@
         <v>DH3整车配置清单</v>
       </c>
       <c r="D3" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/file/R9ZGbDYjxoPqwwxpzNzcfeObnZg?from=from_copylink</v>
+        <v>https://acndoaymjsa1.feishu.cn/file/OIj0bkDXboXH3ExfXg7cbTzOnAh</v>
       </c>
       <c r="E3" t="str">
         <v>url</v>
       </c>
       <c r="F3" t="str" xml:space="preserve">
         <v xml:space="preserve">【飞书】DH3整车配置表
-11月20日版本</v>
+12月3日版本</v>
       </c>
     </row>
     <row r="4">

--- a/table.xlsx
+++ b/table.xlsx
@@ -489,45 +489,45 @@
         <v>【飞书】包含DH1，DH3各业务板块联系人信息</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="str">
+        <v>开发计划</v>
+      </c>
+      <c r="C5" t="str">
+        <v>DH3项目智软控制器开发计划</v>
+      </c>
+      <c r="D5" t="str">
+        <v>https://acndoaymjsa1.feishu.cn/file/K8KlbxqKmoZV2HxoG94ccLotnne</v>
+      </c>
+      <c r="E5" t="str">
+        <v>url</v>
+      </c>
+      <c r="F5" t="str">
+        <v>【飞书】请大家在此更新各自开发计划</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
         <v>设计评审</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C6" t="str">
         <v>DH3电子电气拓扑图</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D6" t="str">
         <v>w:\yling</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E6" t="str">
         <v>folder</v>
       </c>
-      <c r="F5" t="str" xml:space="preserve">
+      <c r="F6" t="str" xml:space="preserve">
         <v xml:space="preserve">【内网】w:\yling
 请确保你的账号已经切换到内网</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>阶段评审</v>
-      </c>
-      <c r="C6" t="str">
-        <v>DH3项目J2阶段评审材料输入信息</v>
-      </c>
-      <c r="D6" t="str">
-        <v>\\10.4.9.25\Project\DH系列\060-整车开发\DH3\J2评审输入</v>
-      </c>
-      <c r="E6" t="str">
-        <v>folder</v>
-      </c>
-      <c r="F6" t="str">
-        <v>【外网】J2阶段输入物数据库</v>
       </c>
     </row>
     <row r="7">
@@ -538,16 +538,16 @@
         <v>阶段评审</v>
       </c>
       <c r="C7" t="str">
-        <v>DH3项目J2阶段评审材料归档路径</v>
+        <v>DH3项目J2阶段评审材料输入信息</v>
       </c>
       <c r="D7" t="str">
-        <v>\\10.4.9.25\Project\DH系列\130-智能软件\DH3\130100_ 阶段评审材料\130102_ J2阶段评审材料及会议纪要</v>
+        <v>\\10.4.9.25\Project\DH系列\060-整车开发\DH3\J2评审输入</v>
       </c>
       <c r="E7" t="str">
         <v>folder</v>
       </c>
       <c r="F7" t="str">
-        <v>【外网】请大家把J2材料及会议纪要放入此文件夹</v>
+        <v>【外网】J2阶段输入物数据库</v>
       </c>
     </row>
     <row r="8">
@@ -555,19 +555,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>开发计划</v>
+        <v>阶段评审</v>
       </c>
       <c r="C8" t="str">
-        <v>DH3项目智软控制器开发计划</v>
+        <v>DH3项目J2阶段评审材料归档路径</v>
       </c>
       <c r="D8" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/file/K8KlbxqKmoZV2HxoG94ccLotnne</v>
+        <v>\\10.4.9.25\Project\DH系列\130-智能软件\DH3\130100_ 阶段评审材料\130102_ J2阶段评审材料及会议纪要</v>
       </c>
       <c r="E8" t="str">
-        <v>url</v>
+        <v>folder</v>
       </c>
       <c r="F8" t="str">
-        <v>【飞书】请大家在此更新各自开发计划</v>
+        <v>【外网】请大家把J2材料及会议纪要放入此文件夹</v>
       </c>
     </row>
     <row r="9">

--- a/table.xlsx
+++ b/table.xlsx
@@ -448,45 +448,45 @@
 12月8日版本</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="str">
+        <v>开发计划</v>
+      </c>
+      <c r="C3" t="str">
+        <v>DH3项目软件基线策划与控制器开发计划</v>
+      </c>
+      <c r="D3" t="str">
+        <v>https://acndoaymjsa1.feishu.cn/slides/Rdl4sdsJslhCQRd7eGbclVidnxe?from=from_copylink</v>
+      </c>
+      <c r="E3" t="str">
+        <v>url</v>
+      </c>
+      <c r="F3" t="str">
+        <v>【飞书】请大家在此更新各自开发计划</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
         <v>整车配置</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C4" t="str">
         <v>DH3整车配置清单</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D4" t="str">
         <v>https://acndoaymjsa1.feishu.cn/file/OIj0bkDXboXH3ExfXg7cbTzOnAh</v>
       </c>
-      <c r="E3" t="str">
-        <v>url</v>
-      </c>
-      <c r="F3" t="str" xml:space="preserve">
+      <c r="E4" t="str">
+        <v>url</v>
+      </c>
+      <c r="F4" t="str" xml:space="preserve">
         <v xml:space="preserve">【飞书】DH3整车配置表
 12月3日版本</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>联系信息</v>
-      </c>
-      <c r="C4" t="str">
-        <v>DH项目整体联系人清单</v>
-      </c>
-      <c r="D4" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/sheets/Gbh8sTDmdhMD9DtZcC2c7trunRe</v>
-      </c>
-      <c r="E4" t="str">
-        <v>url</v>
-      </c>
-      <c r="F4" t="str">
-        <v>【飞书】包含DH1，DH3各业务板块联系人信息</v>
       </c>
     </row>
     <row r="5">
@@ -494,19 +494,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>开发计划</v>
+        <v>联系信息</v>
       </c>
       <c r="C5" t="str">
-        <v>DH3项目智软控制器开发计划</v>
+        <v>DH项目整体联系人清单</v>
       </c>
       <c r="D5" t="str">
-        <v>https://acndoaymjsa1.feishu.cn/file/K8KlbxqKmoZV2HxoG94ccLotnne</v>
+        <v>https://acndoaymjsa1.feishu.cn/sheets/Gbh8sTDmdhMD9DtZcC2c7trunRe</v>
       </c>
       <c r="E5" t="str">
         <v>url</v>
       </c>
       <c r="F5" t="str">
-        <v>【飞书】请大家在此更新各自开发计划</v>
+        <v>【飞书】包含DH1，DH3各业务板块联系人信息</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">

--- a/table.xlsx
+++ b/table.xlsx
@@ -595,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>联系信息</v>
+        <v>责任分工</v>
       </c>
       <c r="C10" t="str">
         <v>DH3项目研发总院智软内部责任分工</v>

--- a/table.xlsx
+++ b/table.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -650,9 +650,29 @@
         <v>【企微】DH3 LLR和PRC再发防止 - 总院级</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>再发防止</v>
+      </c>
+      <c r="C13" t="str">
+        <v>DH3设计类故障再发防止-扩库</v>
+      </c>
+      <c r="D13" t="str">
+        <v>https://dongfengyipai.feishu.cn/sheets/RqFFsAkeRhPgSutRG0tczl1NnPf?sheet=1cmpLH</v>
+      </c>
+      <c r="E13" t="str">
+        <v>url</v>
+      </c>
+      <c r="F13" t="str">
+        <v>【飞书】DH3设计类故障再发防止-扩库</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/table.xlsx
+++ b/table.xlsx
@@ -661,7 +661,7 @@
         <v>DH3设计类故障再发防止-扩库</v>
       </c>
       <c r="D13" t="str">
-        <v>https://dongfengyipai.feishu.cn/sheets/RqFFsAkeRhPgSutRG0tczl1NnPf?sheet=1cmpLH</v>
+        <v>https://dongfengyipai.feishu.cn/sheets/XqPHs0HR2hPAzYt5HumcUJoHnab?sheet=2qDVoG</v>
       </c>
       <c r="E13" t="str">
         <v>url</v>

--- a/table.xlsx
+++ b/table.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -670,9 +670,29 @@
         <v>【飞书】DH3设计类故障再发防止-扩库</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>阶段评审</v>
+      </c>
+      <c r="C14" t="str">
+        <v>DH3异响再发防止清单-各专业</v>
+      </c>
+      <c r="D14" t="str">
+        <v>https://acndoaymjsa1.feishu.cn/wiki/TU8YwzEhgi340zkxqVEcTmQindc</v>
+      </c>
+      <c r="E14" t="str">
+        <v>url</v>
+      </c>
+      <c r="F14" t="str">
+        <v>【飞书】DH3异响再发防止清单-各专业</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/table.xlsx
+++ b/table.xlsx
@@ -675,7 +675,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>阶段评审</v>
+        <v>再发防止</v>
       </c>
       <c r="C14" t="str">
         <v>DH3异响再发防止清单-各专业</v>

--- a/table.xlsx
+++ b/table.xlsx
@@ -675,7 +675,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>再发防止</v>
+        <v>阶段评审</v>
       </c>
       <c r="C14" t="str">
         <v>DH3异响再发防止清单-各专业</v>
